--- a/BOM_CB_BIU_S2v2.0_Changes.xlsx
+++ b/BOM_CB_BIU_S2v2.0_Changes.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\Desktop\New folder\BCU-PCBA-main\BCU-PCBA-main\BCU-PCBA\CARRIER BOARD 2.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\robertMeares-VCU-BCU\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="11115" yWindow="3060" windowWidth="23340" windowHeight="14160" tabRatio="500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="CARRIER_BOARD_S2_V2.0" sheetId="1" r:id="rId1"/>
@@ -1588,7 +1588,7 @@
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* \-??_ ;_-@_ "/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1632,6 +1632,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1717,7 +1724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1835,6 +1842,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2259,7 +2269,7 @@
       <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="43" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="5">
@@ -2320,7 +2330,7 @@
       <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="43" t="s">
         <v>10</v>
       </c>
       <c r="H2" s="5">
@@ -2378,7 +2388,7 @@
       <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="43" t="s">
         <v>16</v>
       </c>
       <c r="H3" s="5">
@@ -2436,7 +2446,7 @@
       <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="43" t="s">
         <v>21</v>
       </c>
       <c r="H4" s="5">
@@ -2494,7 +2504,7 @@
       <c r="F5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="43" t="s">
         <v>27</v>
       </c>
       <c r="H5" s="5">
@@ -2552,7 +2562,7 @@
       <c r="F6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="43" t="s">
         <v>31</v>
       </c>
       <c r="H6" s="5">
@@ -2610,7 +2620,7 @@
       <c r="F7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="43" t="s">
         <v>35</v>
       </c>
       <c r="H7" s="5">
@@ -2668,7 +2678,7 @@
       <c r="F8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="43" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="5">
@@ -2726,7 +2736,7 @@
       <c r="F9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="43" t="s">
         <v>41</v>
       </c>
       <c r="H9" s="5">
@@ -2784,7 +2794,7 @@
       <c r="F10" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="43" t="s">
         <v>45</v>
       </c>
       <c r="H10" s="5">
@@ -2844,7 +2854,7 @@
       <c r="F11" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="43" t="s">
         <v>50</v>
       </c>
       <c r="H11" s="5">
@@ -2902,7 +2912,7 @@
       <c r="F12" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="43" t="s">
         <v>53</v>
       </c>
       <c r="H12" s="5">
@@ -2960,7 +2970,7 @@
       <c r="F13" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="43" t="s">
         <v>57</v>
       </c>
       <c r="H13" s="5">
@@ -3018,7 +3028,7 @@
       <c r="F14" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="43" t="s">
         <v>60</v>
       </c>
       <c r="H14" s="5">
@@ -3076,7 +3086,7 @@
       <c r="F15" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="43" t="s">
         <v>64</v>
       </c>
       <c r="H15" s="5">
@@ -3134,7 +3144,7 @@
       <c r="F16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="43" t="s">
         <v>67</v>
       </c>
       <c r="H16" s="5">
@@ -3192,7 +3202,7 @@
       <c r="F17" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="43" t="s">
         <v>71</v>
       </c>
       <c r="H17" s="5">
@@ -3252,7 +3262,7 @@
       <c r="F18" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="43" t="s">
         <v>74</v>
       </c>
       <c r="H18" s="5">
@@ -3310,7 +3320,7 @@
       <c r="F19" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="43" t="s">
         <v>77</v>
       </c>
       <c r="H19" s="5">
@@ -3368,7 +3378,7 @@
       <c r="F20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="43" t="s">
         <v>81</v>
       </c>
       <c r="H20" s="5">
@@ -3426,7 +3436,7 @@
       <c r="F21" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="43" t="s">
         <v>85</v>
       </c>
       <c r="H21" s="5" t="s">
@@ -3486,7 +3496,7 @@
       <c r="F22" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="43" t="s">
         <v>89</v>
       </c>
       <c r="H22" s="5">
@@ -3544,7 +3554,7 @@
       <c r="F23" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="43" t="s">
         <v>92</v>
       </c>
       <c r="H23" s="5">
@@ -3602,7 +3612,7 @@
       <c r="F24" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="43" t="s">
         <v>16</v>
       </c>
       <c r="H24" s="5">
@@ -3662,7 +3672,7 @@
       <c r="F25" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="43" t="s">
         <v>98</v>
       </c>
       <c r="H25" s="5">
@@ -3720,7 +3730,7 @@
       <c r="F26" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="43" t="s">
         <v>102</v>
       </c>
       <c r="H26" s="5">
@@ -3778,7 +3788,7 @@
       <c r="F27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="43" t="s">
         <v>41</v>
       </c>
       <c r="H27" s="5">
@@ -3836,7 +3846,7 @@
       <c r="F28" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="43" t="s">
         <v>107</v>
       </c>
       <c r="H28" s="5">
@@ -3894,7 +3904,7 @@
       <c r="F29" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="43" t="s">
         <v>112</v>
       </c>
       <c r="H29" s="5">
@@ -3952,7 +3962,7 @@
       <c r="F30" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="43" t="s">
         <v>107</v>
       </c>
       <c r="H30" s="5">
@@ -4012,7 +4022,7 @@
       <c r="F31" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="G31" s="43" t="s">
         <v>118</v>
       </c>
       <c r="H31" s="5">
@@ -4072,7 +4082,7 @@
       <c r="F32" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="43" t="s">
         <v>122</v>
       </c>
       <c r="H32" s="5">
@@ -4130,7 +4140,7 @@
       <c r="F33" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="G33" s="43" t="s">
         <v>126</v>
       </c>
       <c r="H33" s="5">
@@ -4188,7 +4198,7 @@
       <c r="F34" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="43" t="s">
         <v>131</v>
       </c>
       <c r="H34" s="5" t="s">
@@ -4246,7 +4256,7 @@
       <c r="F35" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="G35" s="43" t="s">
         <v>135</v>
       </c>
       <c r="H35" s="5" t="s">
@@ -4304,7 +4314,7 @@
       <c r="F36" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="43" t="s">
         <v>139</v>
       </c>
       <c r="H36" s="5" t="s">
@@ -4362,7 +4372,7 @@
       <c r="F37" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="43" t="s">
         <v>145</v>
       </c>
       <c r="H37" s="5" t="s">
@@ -4420,7 +4430,7 @@
       <c r="F38" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="43" t="s">
         <v>148</v>
       </c>
       <c r="H38" s="5" t="s">
@@ -4478,7 +4488,7 @@
       <c r="F39" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="G39" s="43" t="s">
         <v>153</v>
       </c>
       <c r="H39" s="5" t="s">
@@ -4536,7 +4546,7 @@
       <c r="F40" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="43" t="s">
         <v>161</v>
       </c>
       <c r="H40" s="5" t="s">
@@ -4653,7 +4663,7 @@
       <c r="F42" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="43" t="s">
         <v>170</v>
       </c>
       <c r="H42" s="5">
@@ -9108,7 +9118,7 @@
     <hyperlink ref="D58" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/BOM_CB_BIU_S2v2.0_Changes.xlsx
+++ b/BOM_CB_BIU_S2v2.0_Changes.xlsx
@@ -1724,7 +1724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1845,6 +1845,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4721,7 +4724,7 @@
       <c r="F43" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="43" t="s">
         <v>175</v>
       </c>
       <c r="H43" s="5">
@@ -4779,7 +4782,7 @@
       <c r="F44" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="43" t="s">
         <v>177</v>
       </c>
       <c r="H44" s="5" t="s">
@@ -4837,7 +4840,7 @@
       <c r="F45" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G45" s="5" t="s">
+      <c r="G45" s="43" t="s">
         <v>183</v>
       </c>
       <c r="H45" s="5" t="s">
@@ -4898,7 +4901,7 @@
       <c r="F46" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="43">
         <v>484060003</v>
       </c>
       <c r="H46" s="5" t="s">
@@ -5014,7 +5017,7 @@
       <c r="F48" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="43" t="s">
         <v>196</v>
       </c>
       <c r="H48" s="5" t="s">
@@ -5130,7 +5133,7 @@
       <c r="F50" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G50" s="44" t="s">
         <v>204</v>
       </c>
       <c r="H50" s="5" t="s">
@@ -5188,7 +5191,7 @@
       <c r="F51" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="G51" s="7" t="s">
+      <c r="G51" s="44" t="s">
         <v>207</v>
       </c>
       <c r="H51" s="5" t="s">
@@ -5246,7 +5249,7 @@
       <c r="F52" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="43" t="s">
         <v>215</v>
       </c>
       <c r="H52" s="5" t="s">
@@ -5304,7 +5307,7 @@
       <c r="F53" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="G53" s="5" t="s">
+      <c r="G53" s="43" t="s">
         <v>220</v>
       </c>
       <c r="H53" s="5" t="s">

--- a/BOM_CB_BIU_S2v2.0_Changes.xlsx
+++ b/BOM_CB_BIU_S2v2.0_Changes.xlsx
@@ -1588,7 +1588,7 @@
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* \-??_ ;_-@_ "/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1640,8 +1640,15 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1658,6 +1665,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF6D6D"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFCCFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1724,7 +1737,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1848,6 +1861,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5465,7 +5484,7 @@
       <c r="F56" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="43" t="s">
         <v>231</v>
       </c>
       <c r="H56" s="5">
@@ -5581,7 +5600,7 @@
       <c r="F58" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="43" t="s">
         <v>241</v>
       </c>
       <c r="H58" s="5">
@@ -5639,7 +5658,7 @@
       <c r="F59" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="G59" s="5" t="s">
+      <c r="G59" s="43" t="s">
         <v>243</v>
       </c>
       <c r="H59" s="5" t="s">
@@ -5697,7 +5716,7 @@
       <c r="F60" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="43" t="s">
         <v>247</v>
       </c>
       <c r="H60" s="5" t="s">
@@ -5755,7 +5774,7 @@
       <c r="F61" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G61" s="5" t="s">
+      <c r="G61" s="43" t="s">
         <v>252</v>
       </c>
       <c r="H61" s="5" t="s">
@@ -5813,7 +5832,7 @@
       <c r="F62" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="43" t="s">
         <v>256</v>
       </c>
       <c r="H62" s="5">
@@ -5873,7 +5892,7 @@
       <c r="F63" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G63" s="5" t="s">
+      <c r="G63" s="43" t="s">
         <v>261</v>
       </c>
       <c r="H63" s="5">
@@ -5931,7 +5950,7 @@
       <c r="F64" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="43" t="s">
         <v>265</v>
       </c>
       <c r="H64" s="5">
@@ -5989,7 +6008,7 @@
       <c r="F65" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="G65" s="5" t="s">
+      <c r="G65" s="43" t="s">
         <v>267</v>
       </c>
       <c r="H65" s="5" t="s">
@@ -6047,7 +6066,7 @@
       <c r="F66" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="43" t="s">
         <v>273</v>
       </c>
       <c r="H66" s="5" t="s">
@@ -6105,7 +6124,7 @@
       <c r="F67" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G67" s="5" t="s">
+      <c r="G67" s="43" t="s">
         <v>280</v>
       </c>
       <c r="H67" s="5">
@@ -6165,7 +6184,7 @@
       <c r="F68" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="43" t="s">
         <v>287</v>
       </c>
       <c r="H68" s="5">
@@ -6223,7 +6242,7 @@
       <c r="F69" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G69" s="5" t="s">
+      <c r="G69" s="43" t="s">
         <v>291</v>
       </c>
       <c r="H69" s="5">
@@ -6283,7 +6302,7 @@
       <c r="F70" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" s="43" t="s">
         <v>296</v>
       </c>
       <c r="H70" s="5">
@@ -6341,7 +6360,7 @@
       <c r="F71" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G71" s="5" t="s">
+      <c r="G71" s="43" t="s">
         <v>301</v>
       </c>
       <c r="H71" s="5">
@@ -6401,7 +6420,7 @@
       <c r="F72" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="43" t="s">
         <v>306</v>
       </c>
       <c r="H72" s="5">
@@ -6459,7 +6478,7 @@
       <c r="F73" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G73" s="5" t="s">
+      <c r="G73" s="43" t="s">
         <v>310</v>
       </c>
       <c r="H73" s="5">
@@ -6517,7 +6536,7 @@
       <c r="F74" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="43" t="s">
         <v>314</v>
       </c>
       <c r="H74" s="5">
@@ -6575,7 +6594,7 @@
       <c r="F75" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G75" s="5" t="s">
+      <c r="G75" s="43" t="s">
         <v>318</v>
       </c>
       <c r="H75" s="5">
@@ -6633,7 +6652,7 @@
       <c r="F76" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="43" t="s">
         <v>322</v>
       </c>
       <c r="H76" s="5">
@@ -6691,7 +6710,7 @@
       <c r="F77" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G77" s="5" t="s">
+      <c r="G77" s="43" t="s">
         <v>326</v>
       </c>
       <c r="H77" s="5">
@@ -6749,7 +6768,7 @@
       <c r="F78" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="43" t="s">
         <v>331</v>
       </c>
       <c r="H78" s="5">
@@ -6809,7 +6828,7 @@
       <c r="F79" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G79" s="5" t="s">
+      <c r="G79" s="43" t="s">
         <v>336</v>
       </c>
       <c r="H79" s="5">
@@ -6867,7 +6886,7 @@
       <c r="F80" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="43" t="s">
         <v>340</v>
       </c>
       <c r="H80" s="5">
@@ -6925,7 +6944,7 @@
       <c r="F81" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G81" s="5" t="s">
+      <c r="G81" s="43" t="s">
         <v>344</v>
       </c>
       <c r="H81" s="5">
@@ -6983,7 +7002,7 @@
       <c r="F82" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="43" t="s">
         <v>347</v>
       </c>
       <c r="H82" s="5">
@@ -7041,7 +7060,7 @@
       <c r="F83" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G83" s="5" t="s">
+      <c r="G83" s="43" t="s">
         <v>350</v>
       </c>
       <c r="H83" s="5">
@@ -7101,7 +7120,7 @@
       <c r="F84" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="G84" s="43" t="s">
         <v>354</v>
       </c>
       <c r="H84" s="5">
@@ -7161,7 +7180,7 @@
       <c r="F85" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G85" s="5" t="s">
+      <c r="G85" s="43" t="s">
         <v>350</v>
       </c>
       <c r="H85" s="5">
@@ -7221,7 +7240,7 @@
       <c r="F86" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="G86" s="43" t="s">
         <v>361</v>
       </c>
       <c r="H86" s="5">
@@ -7279,7 +7298,7 @@
       <c r="F87" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="G87" s="5" t="s">
+      <c r="G87" s="43" t="s">
         <v>365</v>
       </c>
       <c r="H87" s="5">
@@ -7337,7 +7356,7 @@
       <c r="F88" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="43" t="s">
         <v>368</v>
       </c>
       <c r="H88" s="5">
@@ -7395,7 +7414,7 @@
       <c r="F89" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G89" s="5" t="s">
+      <c r="G89" s="43" t="s">
         <v>371</v>
       </c>
       <c r="H89" s="5">
@@ -7455,7 +7474,7 @@
       <c r="F90" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="43" t="s">
         <v>376</v>
       </c>
       <c r="H90" s="5">
@@ -7513,7 +7532,7 @@
       <c r="F91" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="G91" s="5" t="s">
+      <c r="G91" s="43" t="s">
         <v>379</v>
       </c>
       <c r="H91" s="5">
@@ -7571,7 +7590,7 @@
       <c r="F92" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="45" t="s">
         <v>383</v>
       </c>
       <c r="H92" s="5" t="s">
@@ -7629,7 +7648,7 @@
       <c r="F93" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="G93" s="5" t="s">
+      <c r="G93" s="46" t="s">
         <v>386</v>
       </c>
       <c r="H93" s="5" t="s">
@@ -7687,7 +7706,7 @@
       <c r="F94" s="5" t="s">
         <v>394</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="46" t="s">
         <v>392</v>
       </c>
       <c r="H94" s="5" t="s">
@@ -7745,7 +7764,7 @@
       <c r="F95" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="G95" s="5" t="s">
+      <c r="G95" s="46" t="s">
         <v>400</v>
       </c>
       <c r="H95" s="5" t="s">
@@ -7803,7 +7822,7 @@
       <c r="F96" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="43" t="s">
         <v>403</v>
       </c>
       <c r="H96" s="5" t="s">
@@ -7904,7 +7923,7 @@
       <c r="F98" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="43" t="s">
         <v>409</v>
       </c>
       <c r="H98" s="5" t="s">
@@ -7962,7 +7981,7 @@
       <c r="F99" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G99" s="5" t="s">
+      <c r="G99" s="43" t="s">
         <v>413</v>
       </c>
       <c r="H99" s="5" t="s">
@@ -8020,7 +8039,7 @@
       <c r="F100" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="43" t="s">
         <v>417</v>
       </c>
       <c r="H100" s="5" t="s">
@@ -8078,7 +8097,7 @@
       <c r="F101" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="G101" s="5" t="s">
+      <c r="G101" s="43" t="s">
         <v>421</v>
       </c>
       <c r="H101" s="5" t="s">
@@ -8193,7 +8212,7 @@
       <c r="F103" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G103" s="5" t="s">
+      <c r="G103" s="43" t="s">
         <v>432</v>
       </c>
       <c r="H103" s="5" t="s">
@@ -8251,7 +8270,7 @@
       <c r="F104" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="43" t="s">
         <v>436</v>
       </c>
       <c r="H104" s="5" t="s">

--- a/BOM_CB_BIU_S2v2.0_Changes.xlsx
+++ b/BOM_CB_BIU_S2v2.0_Changes.xlsx
@@ -1588,7 +1588,7 @@
     <numFmt numFmtId="166" formatCode="_-[$$-409]* #,##0.00_ ;_-[$$-409]* \-#,##0.00\ ;_-[$$-409]* \-??_ ;_-@_ "/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1643,6 +1643,13 @@
     <font>
       <sz val="11"/>
       <color theme="4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1737,7 +1744,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1867,6 +1874,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -8328,7 +8338,7 @@
       <c r="F105" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G105" s="5" t="s">
+      <c r="G105" s="43" t="s">
         <v>440</v>
       </c>
       <c r="H105" s="5" t="s">
@@ -8386,7 +8396,7 @@
       <c r="F106" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="43" t="s">
         <v>446</v>
       </c>
       <c r="H106" s="5" t="s">
@@ -8444,7 +8454,7 @@
       <c r="F107" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="G107" s="5" t="s">
+      <c r="G107" s="43" t="s">
         <v>449</v>
       </c>
       <c r="H107" s="5" t="s">
@@ -8502,7 +8512,7 @@
       <c r="F108" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="43" t="s">
         <v>453</v>
       </c>
       <c r="H108" s="5" t="s">
@@ -8560,7 +8570,7 @@
       <c r="F109" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G109" s="5" t="s">
+      <c r="G109" s="43" t="s">
         <v>457</v>
       </c>
       <c r="H109" s="5" t="s">
@@ -8618,7 +8628,7 @@
       <c r="F110" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="43" t="s">
         <v>461</v>
       </c>
       <c r="H110" s="5" t="s">
@@ -8676,7 +8686,7 @@
       <c r="F111" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="G111" s="5" t="s">
+      <c r="G111" s="43" t="s">
         <v>466</v>
       </c>
       <c r="H111" s="5" t="s">
@@ -8734,7 +8744,7 @@
       <c r="F112" s="5" t="s">
         <v>405</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="43" t="s">
         <v>468</v>
       </c>
       <c r="H112" s="5" t="s">
@@ -8792,7 +8802,7 @@
       <c r="F113" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="G113" s="5" t="s">
+      <c r="G113" s="43" t="s">
         <v>471</v>
       </c>
       <c r="H113" s="5" t="s">
@@ -8850,7 +8860,7 @@
       <c r="F114" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="47" t="s">
         <v>479</v>
       </c>
       <c r="H114" s="5" t="s">
